--- a/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-vent-beatmungsvolumen-min-maschineller-beatmung.xlsx
+++ b/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-vent-beatmungsvolumen-min-maschineller-beatmung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3691" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3691" uniqueCount="572">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T12:10:38+00:00</t>
+    <t>2026-09-15T13:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system = 'http://loinc.org').exists() or coding.where(system = 'http://snomed.info/sct').exists() or coding.where(system = 'http://dgai.de').exists() or coding.where(system = 'urn:iso:std:iso:11073:10101').exists()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -872,6 +872,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system = 'http://loinc.org').exists() or coding.where(system = 'http://snomed.info/sct').exists() or coding.where(system = 'http://dgai.de').exists() or coding.where(system = 'urn:iso:std:iso:11073:10101').exists()}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -5445,30 +5449,30 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>274</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5580,10 +5584,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5697,10 +5701,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5708,7 +5712,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -5814,13 +5818,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>80</v>
@@ -5864,7 +5868,7 @@
         <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>80</v>
@@ -5883,7 +5887,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5933,10 +5937,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6048,10 +6052,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6165,10 +6169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6213,7 +6217,7 @@
         <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>80</v>
@@ -6284,10 +6288,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6401,10 +6405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6518,10 +6522,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6635,10 +6639,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6754,13 +6758,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>80</v>
@@ -6804,7 +6808,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -6823,7 +6827,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6873,10 +6877,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6988,10 +6992,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7105,10 +7109,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7153,7 +7157,7 @@
         <v>80</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>80</v>
@@ -7224,10 +7228,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7341,10 +7345,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7458,10 +7462,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7575,10 +7579,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7694,13 +7698,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>80</v>
@@ -7744,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>80</v>
@@ -7763,7 +7767,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7813,10 +7817,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7928,10 +7932,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8045,10 +8049,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8093,7 +8097,7 @@
         <v>80</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>80</v>
@@ -8164,10 +8168,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8281,10 +8285,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8398,10 +8402,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8515,10 +8519,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8634,10 +8638,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8753,10 +8757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8779,19 +8783,19 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8840,7 +8844,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8855,16 +8859,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8872,10 +8876,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8898,16 +8902,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8957,7 +8961,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8978,10 +8982,10 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8989,14 +8993,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9015,19 +9019,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9076,7 +9080,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9091,16 +9095,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9108,14 +9112,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9134,19 +9138,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9195,7 +9199,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9210,16 +9214,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9227,10 +9231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9253,16 +9257,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9312,7 +9316,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9333,10 +9337,10 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9344,10 +9348,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9370,17 +9374,17 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9429,7 +9433,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9444,16 +9448,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9461,10 +9465,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9487,19 +9491,19 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9509,7 +9513,7 @@
         <v>80</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>80</v>
@@ -9548,7 +9552,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9557,7 +9561,7 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
@@ -9566,24 +9570,24 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9695,10 +9699,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9812,10 +9816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9838,19 +9842,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9899,7 +9903,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9920,7 +9924,7 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>80</v>
@@ -9931,10 +9935,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9960,20 +9964,20 @@
         <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q67" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R67" t="s" s="2">
         <v>80</v>
@@ -9997,10 +10001,10 @@
         <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10018,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10039,7 +10043,7 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
@@ -10050,10 +10054,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10079,14 +10083,14 @@
         <v>196</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10135,7 +10139,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10156,7 +10160,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10167,10 +10171,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10196,14 +10200,14 @@
         <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10213,7 +10217,7 @@
         <v>80</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>80</v>
@@ -10252,7 +10256,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10261,7 +10265,7 @@
         <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>102</v>
@@ -10273,7 +10277,7 @@
         <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>80</v>
@@ -10284,10 +10288,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10313,16 +10317,16 @@
         <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10371,7 +10375,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10392,7 +10396,7 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>80</v>
@@ -10403,10 +10407,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10432,16 +10436,16 @@
         <v>182</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10466,13 +10470,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10490,7 +10494,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10499,7 +10503,7 @@
         <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>102</v>
@@ -10511,7 +10515,7 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>80</v>
@@ -10522,14 +10526,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10551,16 +10555,16 @@
         <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10585,13 +10589,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10609,7 +10613,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10627,24 +10631,24 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10667,19 +10671,19 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10728,7 +10732,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10749,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>80</v>
@@ -10760,10 +10764,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10789,13 +10793,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10821,11 +10825,11 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10843,7 +10847,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10861,24 +10865,24 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10904,16 +10908,16 @@
         <v>182</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -10941,10 +10945,10 @@
         <v>271</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10962,7 +10966,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10983,7 +10987,7 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
@@ -10994,10 +10998,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11020,16 +11024,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11079,7 +11083,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11097,24 +11101,24 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11137,16 +11141,16 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11196,7 +11200,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11214,24 +11218,24 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11254,19 +11258,19 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11315,7 +11319,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11327,7 +11331,7 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
@@ -11336,7 +11340,7 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
@@ -11347,10 +11351,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11462,10 +11466,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11579,14 +11583,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11608,10 +11612,10 @@
         <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>137</v>
@@ -11666,7 +11670,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11698,10 +11702,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11724,13 +11728,13 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11781,7 +11785,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11790,7 +11794,7 @@
         <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>102</v>
@@ -11802,7 +11806,7 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>80</v>
@@ -11813,10 +11817,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11839,13 +11843,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11896,7 +11900,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11905,7 +11909,7 @@
         <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>102</v>
@@ -11917,7 +11921,7 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>80</v>
@@ -11928,10 +11932,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11957,16 +11961,16 @@
         <v>182</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11994,10 +11998,10 @@
         <v>114</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -12015,7 +12019,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12033,10 +12037,10 @@
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>80</v>
@@ -12047,10 +12051,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12076,16 +12080,16 @@
         <v>182</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12113,10 +12117,10 @@
         <v>271</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12134,7 +12138,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12152,10 +12156,10 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12166,10 +12170,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12192,17 +12196,17 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12251,7 +12255,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12283,10 +12287,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12312,10 +12316,10 @@
         <v>196</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12366,7 +12370,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12387,7 +12391,7 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
@@ -12398,10 +12402,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12424,16 +12428,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12483,7 +12487,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12504,7 +12508,7 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
@@ -12515,10 +12519,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12541,16 +12545,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12600,7 +12604,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12621,7 +12625,7 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -12632,10 +12636,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12658,19 +12662,19 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12719,7 +12723,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12740,7 +12744,7 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -12751,10 +12755,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12866,10 +12870,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12983,14 +12987,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13012,10 +13016,10 @@
         <v>134</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>137</v>
@@ -13070,7 +13074,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13102,10 +13106,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13131,13 +13135,13 @@
         <v>182</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>270</v>
@@ -13189,7 +13193,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>90</v>
@@ -13207,13 +13211,13 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13221,10 +13225,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13247,19 +13251,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13308,7 +13312,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13326,24 +13330,24 @@
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13369,16 +13373,16 @@
         <v>182</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13403,13 +13407,13 @@
         <v>80</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>80</v>
@@ -13427,7 +13431,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13436,7 +13440,7 @@
         <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>102</v>
@@ -13448,7 +13452,7 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>80</v>
@@ -13459,14 +13463,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13488,16 +13492,16 @@
         <v>182</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -13522,13 +13526,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -13546,7 +13550,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13564,24 +13568,24 @@
         <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13607,16 +13611,16 @@
         <v>81</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -13665,7 +13669,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13686,7 +13690,7 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
